--- a/static/auto_sheets/Field Samples Template.xlsx
+++ b/static/auto_sheets/Field Samples Template.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH1"/>
+  <dimension ref="A1:AR1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,169 +436,203 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Sampling depth reference</t>
+          <t>Broad-Scale Environmental Context</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Sample storage location</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Sample storage setting</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Sample storage address</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Sample storage setting</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Elevation (meters)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Environmental Medium</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Sample type</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Water depth (m)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Site Type</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Local Environmental Context</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Longitude</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Sample storage location</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Latitude</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Sample type</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Country/Ocean</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>QR Code</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Region/Province/State</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Age Estimate (to, KABP)</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Sampling depth estimation (bottom, cm)</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Link to other relevant data</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Link to images</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Miscellaneous Environmental Measurements or Observations</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Miscellaneous Sample Measurements or Observations</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Disposal date</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Storing date</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Miscellaneous Sample Measurements or Observations</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Miscellaneous Environmental Measurements or Observations</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Height above mean sea level (meters)</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Age Estimate (ka)</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>PI (KU ID)</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Age Estimate (from, KABP)</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Period Estimate</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Link to images</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Marine isotope stage estimate</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Sediment type</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Sampling Date</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Correlation depth (top, cm)</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Link to other relevant data</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Correlation depth (bottom, cm)</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>Sampling depth (interval, cm)</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>Sample provider(s)</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>Sampling depth estimation (top, cm)</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>Sampling depth (discrete, cm)</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>Running Project Title</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>PI (KU ID)</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>Sample provider(s)</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>Sampling Date</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>Sampling site</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>City/Town/Location</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>Country/Ocean</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>QR Code</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>Sediment type</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>Comment</t>
-        </is>
-      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>City/Town/Lake/Location</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>Sampling Site</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr"/>
+      <c r="AP1" s="1" t="inlineStr"/>
+      <c r="AQ1" s="1" t="inlineStr"/>
+      <c r="AR1" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
